--- a/out/MLP-mamba2_repeat_1_000002.xlsx
+++ b/out/MLP-mamba2_repeat_1_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.503542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7867500136927614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.503542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.103542575915647</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.503542575915647</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000002.xlsx
+++ b/out/MLP-mamba2_repeat_1_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.2057574499049892</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.503542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.503542575915647</v>
+        <v>0.2057574499049892</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000002.xlsx
+++ b/out/MLP-mamba2_repeat_1_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.274958997964859</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.2057574499049892</v>
+        <v>-0.7199999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.6453896164894104</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.2920740246772766</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4339184463024139</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5567536354064941</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5334997177124023</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3986068665981293</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.6553891897201538</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.7516134977340698</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2419456243515015</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4265497624874115</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3872794508934021</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6287106275558472</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3845786452293396</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4661854803562164</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3942951560020447</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4218066334724426</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4262504875659943</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4150521457195282</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5498093366622925</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3688932657241821</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3962458074092865</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5852000093893223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4677910208702087</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.8832723498344421</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.2697616517543793</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5953691005706787</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5133450627326965</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5624042153358459</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3813098669052124</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.3985649645328522</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4383043944835663</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.454925000667572</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4828962981700897</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4998592436313629</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.6630879044532776</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.536076603003093</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7508488297462463</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5344902276992798</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5450276136398315</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6832794547080994</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6745248436927795</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8417885303497314</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8465522527694702</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5537059307098389</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.396714909199301</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.9314940571784973</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.0114743709564209</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.2992812395095825</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2172896564006805</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5679721832275391</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3219885230064392</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.9032107591629028</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.1404279619455338</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4232907295227051</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.2276242673397064</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.43031045794487</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5699936747550964</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2821082174777985</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4922332763671875</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.6616473793983459</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3633368909358978</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5097720623016357</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.638898491859436</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3182937204837799</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3565086722373962</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6729280352592468</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.536076603003093</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.6436346769332886</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7304009199142456</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2145932912826538</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.2337674647569656</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3524532914161682</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3553018271923065</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3712281882762909</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2750912606716156</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.5493119955062866</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.344884991645813</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4084099531173706</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3824746906757355</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.324699878692627</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4077142775058746</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4313812255859375</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5124452114105225</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.5003892183303833</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.396714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6102659702301025</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.396714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.513340950012207</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.396714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.528802752494812</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3146223425865173</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3636353611946106</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.6307851672172546</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3263302743434906</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6252663135528564</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4467445909976959</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5119329690933228</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3214021027088165</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.2989694178104401</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3461669385433197</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3912590146064758</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4039539396762848</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3791020214557648</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3814571797847748</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4605032503604889</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4159963428974152</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3669354319572449</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5238749980926514</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3982904255390167</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3850975632667542</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4137085676193237</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3933202922344208</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4186578989028931</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4844933450222015</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4123352766036987</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.437784343957901</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.3</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.4061205387115479</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4821112155914307</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6110498905181885</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4244997799396515</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5403105020523071</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5972254872322083</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.396714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.5399225354194641</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.396714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.88846355676651</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1454373449087143</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7693751454353333</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3027946650981903</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.431424617767334</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3707127273082733</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.452018529176712</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.2299999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.7850376963615417</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2057574499049892</v>
+        <v>0.1200000000000004</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000002.xlsx
+++ b/out/MLP-mamba2_repeat_1_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.274958997964859</v>
+        <v>0.2749584913253784</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.7199999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.6453896164894104</v>
+        <v>0.6453897356987</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.5799999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.2920740246772766</v>
+        <v>0.2920739948749542</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.4339184463024139</v>
+        <v>0.4339179694652557</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.1600000000000001</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.5567536354064941</v>
+        <v>0.5567536950111389</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.5334997177124023</v>
+        <v>0.5334991812705994</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3986068665981293</v>
+        <v>0.3986063301563263</v>
       </c>
       <c r="JB8" t="n">
         <v>0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.6553891897201538</v>
+        <v>0.6553893089294434</v>
       </c>
       <c r="JB9" t="n">
         <v>0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4265497624874115</v>
+        <v>0.4265492558479309</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3872794508934021</v>
+        <v>0.3872788846492767</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.6287106275558472</v>
+        <v>0.628710150718689</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3845786452293396</v>
+        <v>0.3845781981945038</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.4661854803562164</v>
+        <v>0.4661850333213806</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.3942951560020447</v>
+        <v>0.3942947089672089</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4218066334724426</v>
+        <v>0.4218061864376068</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4262504875659943</v>
+        <v>0.4262499809265137</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4150521457195282</v>
+        <v>0.4150516390800476</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.5498093366622925</v>
+        <v>0.5498088002204895</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.1199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3688932657241821</v>
+        <v>0.3688928484916687</v>
       </c>
       <c r="JB22" t="n">
         <v>0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3962458074092865</v>
+        <v>0.3962453007698059</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4677910208702087</v>
+        <v>0.4677904844284058</v>
       </c>
       <c r="JB24" t="n">
         <v>0.1600000000000001</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3813098669052124</v>
+        <v>0.3813092410564423</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.3985649645328522</v>
+        <v>0.3985644280910492</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4383043944835663</v>
+        <v>0.4383038580417633</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.8599999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.454925000667572</v>
+        <v>0.4549245238304138</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4828962981700897</v>
+        <v>0.4828957915306091</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4998592436313629</v>
+        <v>0.4998586475849152</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.02000000000000007</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.6630879044532776</v>
+        <v>0.6630879640579224</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.7508488297462463</v>
+        <v>0.7508488893508911</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.6832794547080994</v>
+        <v>0.6832793951034546</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.8417885303497314</v>
+        <v>0.8417884707450867</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.9314940571784973</v>
+        <v>0.9314941763877869</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0114743709564209</v>
+        <v>0.01147430669516325</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.2992812395095825</v>
+        <v>0.2992804944515228</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.2172896564006805</v>
+        <v>0.2172894924879074</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.5679721832275391</v>
+        <v>0.56797194480896</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.4399999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3219885230064392</v>
+        <v>0.3219884634017944</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.9032107591629028</v>
+        <v>0.9032105803489685</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.4399999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1404279619455338</v>
+        <v>0.1404279470443726</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4232907295227051</v>
+        <v>0.4232906401157379</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.2276242673397064</v>
+        <v>0.22762431204319</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.8599999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.43031045794487</v>
+        <v>0.4303104877471924</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.5699936747550964</v>
+        <v>0.5699936151504517</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3182937204837799</v>
+        <v>0.3182937502861023</v>
       </c>
       <c r="JB63" t="n">
         <v>0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.6436346769332886</v>
+        <v>0.643634557723999</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.7304009199142456</v>
+        <v>0.7304008603096008</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.344884991645813</v>
+        <v>0.3448850214481354</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.4084099531173706</v>
+        <v>0.4084096550941467</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3824746906757355</v>
+        <v>0.3824743628501892</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.324699878692627</v>
+        <v>0.3246996402740479</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.4077142775058746</v>
+        <v>0.4077139496803284</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4313812255859375</v>
+        <v>0.431380957365036</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5124452114105225</v>
+        <v>0.5124449133872986</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.5003892183303833</v>
+        <v>0.5003889799118042</v>
       </c>
       <c r="JB82" t="n">
         <v>0.8599999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6102659702301025</v>
+        <v>0.6102660298347473</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.513340950012207</v>
+        <v>0.5133406519889832</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.528802752494812</v>
+        <v>0.5288024544715881</v>
       </c>
       <c r="JB85" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3146223425865173</v>
+        <v>0.3146220445632935</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3636353611946106</v>
+        <v>0.3636350035667419</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.6307851672172546</v>
+        <v>0.630784809589386</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3263302743434906</v>
+        <v>0.326330304145813</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4467445909976959</v>
+        <v>0.4467446208000183</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5119329690933228</v>
+        <v>0.5119326710700989</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3214021027088165</v>
+        <v>0.3214021623134613</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.2989694178104401</v>
+        <v>0.2989691495895386</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3461669385433197</v>
+        <v>0.3461667001247406</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.8599999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3912590146064758</v>
+        <v>0.3912586569786072</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.4039539396762848</v>
+        <v>0.403954029083252</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3791020214557648</v>
+        <v>0.3791016042232513</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.3814571797847748</v>
+        <v>0.3814568221569061</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4605032503604889</v>
+        <v>0.4605027437210083</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.1199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.4159963428974152</v>
+        <v>0.4159964323043823</v>
       </c>
       <c r="JB101" t="n">
         <v>0.16</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3669354319572449</v>
+        <v>0.3669349849224091</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.5238749980926514</v>
+        <v>0.5238745808601379</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.3982904255390167</v>
+        <v>0.3982899785041809</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3850975632667542</v>
+        <v>0.3850971460342407</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4137085676193237</v>
+        <v>0.4137081503868103</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.3933202922344208</v>
+        <v>0.3933199346065521</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.4186578989028931</v>
+        <v>0.4186573922634125</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4844933450222015</v>
+        <v>0.4844928383827209</v>
       </c>
       <c r="JB109" t="n">
         <v>0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4123352766036987</v>
+        <v>0.4123348593711853</v>
       </c>
       <c r="JB110" t="n">
         <v>0.02000000000000007</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.437784343957901</v>
+        <v>0.4377838671207428</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.4061205387115479</v>
+        <v>0.4061201512813568</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.4821112155914307</v>
+        <v>0.4821107685565948</v>
       </c>
       <c r="JB113" t="n">
         <v>0.4399999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.6110498905181885</v>
+        <v>0.611049473285675</v>
       </c>
       <c r="JB114" t="n">
         <v>0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4244997799396515</v>
+        <v>0.4244993329048157</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.5403105020523071</v>
+        <v>0.5403100252151489</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.5972254872322083</v>
+        <v>0.5972256064414978</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.5399225354194641</v>
+        <v>0.5399225950241089</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1454373449087143</v>
+        <v>0.1454373747110367</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.7693751454353333</v>
+        <v>0.769375205039978</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.431424617767334</v>
+        <v>0.4314246475696564</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3707127273082733</v>
+        <v>0.3707127869129181</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.452018529176712</v>
+        <v>0.4520184993743896</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.2299999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.7850376963615417</v>
+        <v>0.7850375771522522</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1200000000000004</v>
